--- a/metadata/plate_metadata/20260324_cep290_24hpf_plate02_well_metadata.xlsx
+++ b/metadata/plate_metadata/20260324_cep290_24hpf_plate02_well_metadata.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -1059,27 +1059,27 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1306,6 +1306,18 @@
       <c r="L9" s="8" t="n"/>
       <c r="M9" s="8" t="n"/>
     </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="H22" s="15" t="n"/>
     </row>
